--- a/result/ablation_result.xlsx
+++ b/result/ablation_result.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="22530" windowHeight="6855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,19 +49,13 @@
     <t>PR-AUC</t>
   </si>
   <si>
-    <t>w/o Random Walk</t>
-  </si>
-  <si>
     <t>w/o DFS</t>
   </si>
   <si>
     <t>w/o BFS</t>
   </si>
   <si>
-    <t>DPGNNPAM</t>
-  </si>
-  <si>
-    <t>w/o Prototypical Network</t>
+    <t>w/o Random Walk</t>
   </si>
   <si>
     <r>
@@ -83,26 +77,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>ssls</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>sslp</t>
     </r>
   </si>
   <si>
@@ -148,6 +122,32 @@
       </rPr>
       <t>ssls</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sslp</t>
+    </r>
+  </si>
+  <si>
+    <t>w/o Prototypical Network</t>
+  </si>
+  <si>
+    <t>DPGNNPAM</t>
   </si>
 </sst>
 </file>
@@ -771,15 +771,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1095,11 +1101,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17.6166666666667" style="1" customWidth="1"/>
-    <col min="2" max="6" width="9" style="1"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="9" style="2"/>
+    <col min="4" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1109,7 +1117,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1126,161 +1134,164 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
-        <v>0.8098</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.8054</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.6447</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.8593</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.6794</v>
+      <c r="B2" s="3">
+        <v>0.85964</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.87816</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.91678</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.8062</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.74628</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
-        <v>0.85964</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.87816</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.91678</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.8062</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.74628</v>
+      <c r="B3" s="3">
+        <v>0.86622</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.8771</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.8329</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.8408</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.71968</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
-        <v>0.86622</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.8771</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.8329</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.8408</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.71968</v>
+      <c r="B4" s="3">
+        <v>0.8098</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.8054</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.6447</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.8593</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.6794</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2">
-        <v>0.8862</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.89866</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.9173</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.8759</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.7934</v>
+      <c r="B5" s="3">
+        <v>0.84086</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.8415</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.83198</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.83888</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.74418</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
-        <v>0.88218</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.89384</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.8781</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.8457</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.75076</v>
+      <c r="B6" s="3">
+        <v>0.8472</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.8523</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.6971</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.80698</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.66724</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
-        <v>0.80698</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="B7" s="3">
+        <v>0.88218</v>
+      </c>
+      <c r="C7" s="4">
         <v>0.81132</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>0.70438</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>0.78292</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>0.61542</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2">
-        <v>0.8472</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.8523</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.6971</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="B8" s="3">
         <v>0.80698</v>
       </c>
-      <c r="F8" s="2">
-        <v>0.66724</v>
+      <c r="C8" s="4">
+        <v>0.89384</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.8781</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.8457</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.75076</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2">
-        <v>0.84086</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.8415</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.83198</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.83888</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.74418</v>
-      </c>
+      <c r="B9" s="3">
+        <v>0.8862</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.89866</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.9173</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.8759</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.7934</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
